--- a/TestCasesRepo/GmailTestCases.xlsx
+++ b/TestCasesRepo/GmailTestCases.xlsx
@@ -4,26 +4,676 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="105" windowWidth="14295" windowHeight="4635"/>
+    <workbookView xWindow="480" yWindow="105" windowWidth="14295" windowHeight="4635" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Traditional Test Cases" sheetId="1" r:id="rId1"/>
+    <sheet name="BDD Style Test Cases" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="86">
+  <si>
+    <t>TC ID</t>
+  </si>
+  <si>
+    <t>Test Scenario</t>
+  </si>
+  <si>
+    <t>Preconditions</t>
+  </si>
+  <si>
+    <t>Test Steps</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>TC_001</t>
+  </si>
+  <si>
+    <t>Verify user can open Gmail compose window</t>
+  </si>
+  <si>
+    <t>User logged into Gmail</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. After user logged in successfully into gmail, should click on compose button
+2. A pop up window at the bottom right should open
+3. When tried to enter values in All the editable fields it should allow
+4. By default the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">From </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>field is filled with composer email details and should be non editable</t>
+    </r>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Compose popup should open successfully</t>
+  </si>
+  <si>
+    <t>TC_002</t>
+  </si>
+  <si>
+    <t>Verify user can enter valid recipient email</t>
+  </si>
+  <si>
+    <t>Compose email window open</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. When user enters a valid Email Id it should accept the id in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">To </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> field.
+2. When user enters a valid Email Id it should accept the id in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  field.
+3. When user enters a valid Email Id it should accept the id in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BCC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  field.</t>
+    </r>
+  </si>
+  <si>
+    <t>testuser@gmail.com</t>
+  </si>
+  <si>
+    <t>Email ID should be accepted</t>
+  </si>
+  <si>
+    <t>Test Case</t>
+  </si>
+  <si>
+    <t>Opening the Compse Window</t>
+  </si>
+  <si>
+    <t>When valid credentials entered in all the 3(To, CC, BCC) fields</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. When user enters an invalid Email Id in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>To</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> an error message should pop-up
+2. When user enters an invalid Email Id in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> an error message should pop-up.
+3. When user enters an invalid Email Id in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BCC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> an error message should pop-up.</t>
+    </r>
+  </si>
+  <si>
+    <t>testuser</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">An error message should be popped up and mention where the invalid email is present, whether in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">To, CC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> BCC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> fields.</t>
+    </r>
+  </si>
+  <si>
+    <t>When invalid credentials entered in reciepent fields</t>
+  </si>
+  <si>
+    <t>Verify Subject field accepts text</t>
+  </si>
+  <si>
+    <t>TC_003</t>
+  </si>
+  <si>
+    <t>TC_004</t>
+  </si>
+  <si>
+    <t>Verify email body accepts text</t>
+  </si>
+  <si>
+    <t>When email id contains special characters (@,!,$)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. When user enters a Email Id with special characters it should accept the id in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">To </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> field.
+2. When user enters a Email Id with special characters it should accept the id in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  field.
+3.  When user enters a Email Id with special characters it should accept the id in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BCC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  field.</t>
+    </r>
+  </si>
+  <si>
+    <t>testuser@@gmail.com</t>
+  </si>
+  <si>
+    <t>Email Id field case sensitivity</t>
+  </si>
+  <si>
+    <t>When email id is entered without any case sensitivity</t>
+  </si>
+  <si>
+    <t>TestUser@GMAIL.com</t>
+  </si>
+  <si>
+    <t>Email ID should be changed to lower case irrespective of any case it entered</t>
+  </si>
+  <si>
+    <t>Incubyte</t>
+  </si>
+  <si>
+    <t>Subject should be entered correctly</t>
+  </si>
+  <si>
+    <t>Entered value in subject field</t>
+  </si>
+  <si>
+    <t>No value entered in subject field</t>
+  </si>
+  <si>
+    <t>1. Leave the subject field empty.
+2. Click on send button.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. A warning message should pop-up stating subject field is empty.
+2. When clicked on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OK, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>it should send the mail successfully.</t>
+    </r>
+  </si>
+  <si>
+    <t>Entered value in body field</t>
+  </si>
+  <si>
+    <t>Enter text in body field</t>
+  </si>
+  <si>
+    <t>Enter text in subject field</t>
+  </si>
+  <si>
+    <t>QA test for Incubyte</t>
+  </si>
+  <si>
+    <t>1. Leave the body field empty.
+2. Click on send button.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. A warning message should pop-up stating body field is empty.
+2. When clicked on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OK, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>it should send the mail successfully.</t>
+    </r>
+  </si>
+  <si>
+    <t>Content in body should be entered correctly</t>
+  </si>
+  <si>
+    <t>TC_005</t>
+  </si>
+  <si>
+    <t>Recipient, subject, and body entered</t>
+  </si>
+  <si>
+    <t>Valid data</t>
+  </si>
+  <si>
+    <t>1. Email should be sent successfully
+2. A success message pop up appears</t>
+  </si>
+  <si>
+    <t>Click Send button
+(or)
+Press Ctrl+Enter button</t>
+  </si>
+  <si>
+    <t>Verify email sends successfully</t>
+  </si>
+  <si>
+    <t>Sending the email when all the fields are entered</t>
+  </si>
+  <si>
+    <t>Sending the email when only reciepent fields are entered</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. A warning message stating no values entered in Subject and Body fields.
+2. When clicked on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OK, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>email should sent.
+3. Email should be sent successfully.
+4. A success message pop up appears.</t>
+    </r>
+  </si>
+  <si>
+    <t>Recipient field is entered</t>
+  </si>
+  <si>
+    <t>Verify sent email appears in Sent folder</t>
+  </si>
+  <si>
+    <t>Email already sent</t>
+  </si>
+  <si>
+    <t>Open Sent folder</t>
+  </si>
+  <si>
+    <t>Sent email should be available in Sent items</t>
+  </si>
+  <si>
+    <t>TC_006</t>
+  </si>
+  <si>
+    <t>Verify internet interruption during send</t>
+  </si>
+  <si>
+    <t>Internet disconnected</t>
+  </si>
+  <si>
+    <t>Try sending email</t>
+  </si>
+  <si>
+    <t>Appropriate error/retry message should display</t>
+  </si>
+  <si>
+    <t>TC_007</t>
+  </si>
+  <si>
+    <t>TC_008</t>
+  </si>
+  <si>
+    <t>Verify draft auto-save functionality</t>
+  </si>
+  <si>
+    <t>Compose mail partially written</t>
+  </si>
+  <si>
+    <t>When data is entered in the compose mail window</t>
+  </si>
+  <si>
+    <t>1. Enter the valid data in the compose window.
+2. Close the window</t>
+  </si>
+  <si>
+    <t>Partial content</t>
+  </si>
+  <si>
+    <t>Draft should auto-save successfully</t>
+  </si>
+  <si>
+    <t>Given the user is logged into Gmail
+When the user clicks on Compose
+And enters a valid recipient email
+And enters subject as "Incubyte"
+And enters body as "QA test for Incubyte"
+And clicks on Send
+Then the email should be sent successfully
+And a confirmation message should appear</t>
+  </si>
+  <si>
+    <t>Scenario 1: Successful email send</t>
+  </si>
+  <si>
+    <t>Scenario 2: Send email without recipient</t>
+  </si>
+  <si>
+    <t>Scenario 3: Invalid email format</t>
+  </si>
+  <si>
+    <t>Scenario 4: Verify draft auto-save</t>
+  </si>
+  <si>
+    <t>Scenario 5: Send email with empty subject</t>
+  </si>
+  <si>
+    <t>Given the user is on the Compose screen
+When the user enters subject as "Incubyte"
+And enters body as "QA test for Incubyte"
+And clicks on Send
+Then the system should display recipient validation error</t>
+  </si>
+  <si>
+    <t>Given the user is on the Compose screen
+When the user enters invalid email address "abc@"
+And clicks on Send
+Then the system should display invalid email format error</t>
+  </si>
+  <si>
+    <t>Given the user is composing an email
+When the user enters subject and body
+And waits for a few seconds without sending
+Then the email draft should be auto-saved</t>
+  </si>
+  <si>
+    <t>Given the user is on the Compose screen
+When the user enters valid recipient email
+And leaves subject empty
+And enters body as "QA test for Incubyte"
+And clicks on Send
+Then the email should be sent or warning should be displayed</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +684,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,14 +692,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -342,27 +1031,399 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.42578125" customWidth="1"/>
+    <col min="5" max="5" width="37.42578125" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="44.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="135">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="90">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="90">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="135">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="60">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="60">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="45">
+      <c r="A11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="90">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="45">
+      <c r="A15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F3" r:id="rId1"/>
+    <hyperlink ref="F6" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="51.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="120">
+      <c r="A2" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="90">
+      <c r="A5" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="75">
+      <c r="A8" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="60">
+      <c r="A11" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="105">
+      <c r="A14" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/TestCasesRepo/GmailTestCases.xlsx
+++ b/TestCasesRepo/GmailTestCases.xlsx
@@ -715,11 +715,8 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -732,8 +729,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1043,315 +1044,315 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="135">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="90">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="135">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="60">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="2"/>
+      <c r="G8" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="60">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3" t="s">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="45">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="90">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3" t="s">
+    <row r="12" spans="1:7" ht="75">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3" t="s">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="45">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1374,52 +1375,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="120">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>76</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="7"/>
+    </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="90">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>82</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="7"/>
+    </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="75">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="6" t="s">
         <v>83</v>
       </c>
     </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="7"/>
+    </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="60">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>84</v>
       </c>
     </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="7"/>
+    </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="105">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="6" t="s">
         <v>85</v>
       </c>
     </row>
